--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2019_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2019_tarapaca.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:04</t>
+    <t xml:space="preserve">2026-09-24 00:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -561,7 +561,7 @@
         <v>-0.37</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>-0.43</v>
@@ -584,7 +584,7 @@
         <v>-0.58</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>-0.35</v>
@@ -607,7 +607,7 @@
         <v>-0.28</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>-0.55</v>
@@ -630,7 +630,7 @@
         <v>0.26</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0.62</v>
@@ -653,7 +653,7 @@
         <v>0.39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0.39</v>
@@ -673,13 +673,13 @@
         <v>6</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-0.83</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="8">
@@ -696,13 +696,13 @@
         <v>6</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="9">
@@ -719,13 +719,13 @@
         <v>6</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="10">
@@ -745,7 +745,7 @@
         <v>0.11</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.41</v>
@@ -768,7 +768,7 @@
         <v>0.1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>-0.4</v>
@@ -791,7 +791,7 @@
         <v>0.26</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0.17</v>
@@ -814,7 +814,7 @@
         <v>0.3</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0.38</v>
@@ -834,10 +834,10 @@
         <v>6</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>-0.28</v>
@@ -857,13 +857,13 @@
         <v>6</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="16">
@@ -883,7 +883,7 @@
         <v>-0.24</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>-0.38</v>
@@ -906,7 +906,7 @@
         <v>-0.36</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>-0.43</v>
@@ -929,7 +929,7 @@
         <v>-0.79</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0.47</v>
@@ -949,13 +949,13 @@
         <v>7</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="20">
@@ -972,13 +972,13 @@
         <v>7</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="21">
@@ -998,7 +998,7 @@
         <v>0.02</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0.36</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2019_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2019_tarapaca.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:55</t>
+    <t xml:space="preserve">2026-10-01 23:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2019_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2019_tarapaca.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:20</t>
+    <t xml:space="preserve">2026-10-05 19:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
